--- a/data/datasets_produtos/ilheus/farinha_ilheus.xlsx
+++ b/data/datasets_produtos/ilheus/farinha_ilheus.xlsx
@@ -2942,7 +2942,12 @@
       </c>
     </row>
     <row r="254" ht="15.75" customHeight="1">
-      <c r="A254" s="6"/>
+      <c r="A254" s="6">
+        <v>46387</v>
+      </c>
+      <c r="B254">
+        <v>24.149999999999999</v>
+      </c>
     </row>
     <row r="255" ht="15.75" customHeight="1">
       <c r="A255" s="6"/>

--- a/data/datasets_produtos/ilheus/farinha_ilheus.xlsx
+++ b/data/datasets_produtos/ilheus/farinha_ilheus.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="110">
   <si>
     <t>ano</t>
   </si>
@@ -343,6 +343,9 @@
   </si>
   <si>
     <t>31-11-2025</t>
+  </si>
+  <si>
+    <t>31-02-2026</t>
   </si>
 </sst>
 </file>
@@ -383,7 +386,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -396,6 +399,9 @@
       <alignment horizontal="right"/>
     </xf>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -2942,15 +2948,20 @@
       </c>
     </row>
     <row r="254" ht="15.75" customHeight="1">
-      <c r="A254" s="6">
-        <v>46387</v>
+      <c r="A254" s="7">
+        <v>46053</v>
       </c>
       <c r="B254">
         <v>24.149999999999999</v>
       </c>
     </row>
     <row r="255" ht="15.75" customHeight="1">
-      <c r="A255" s="6"/>
+      <c r="A255" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="B255">
+        <v>24.600000000000001</v>
+      </c>
     </row>
     <row r="256" ht="15.75" customHeight="1">
       <c r="A256" s="6"/>

--- a/data/datasets_produtos/ilheus/farinha_ilheus.xlsx
+++ b/data/datasets_produtos/ilheus/farinha_ilheus.xlsx
@@ -386,7 +386,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -399,9 +399,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -2948,7 +2945,7 @@
       </c>
     </row>
     <row r="254" ht="15.75" customHeight="1">
-      <c r="A254" s="7">
+      <c r="A254" s="6">
         <v>46053</v>
       </c>
       <c r="B254">
@@ -2956,7 +2953,7 @@
       </c>
     </row>
     <row r="255" ht="15.75" customHeight="1">
-      <c r="A255" s="7" t="s">
+      <c r="A255" s="6" t="s">
         <v>109</v>
       </c>
       <c r="B255">
@@ -2964,7 +2961,12 @@
       </c>
     </row>
     <row r="256" ht="15.75" customHeight="1">
-      <c r="A256" s="6"/>
+      <c r="A256" s="6">
+        <v>46112</v>
+      </c>
+      <c r="B256">
+        <v>23.489999999999998</v>
+      </c>
     </row>
     <row r="257" ht="15.75" customHeight="1">
       <c r="A257" s="6"/>

--- a/data/datasets_produtos/ilheus/farinha_ilheus.xlsx
+++ b/data/datasets_produtos/ilheus/farinha_ilheus.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="111">
   <si>
     <t>ano</t>
   </si>
@@ -346,6 +346,9 @@
   </si>
   <si>
     <t>31-02-2026</t>
+  </si>
+  <si>
+    <t>31-04-2026</t>
   </si>
 </sst>
 </file>
@@ -386,7 +389,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -400,6 +403,9 @@
     </xf>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -2969,7 +2975,12 @@
       </c>
     </row>
     <row r="257" ht="15.75" customHeight="1">
-      <c r="A257" s="6"/>
+      <c r="A257" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="B257" s="7">
+        <v>24.719999999999999</v>
+      </c>
     </row>
     <row r="258" ht="15.75" customHeight="1">
       <c r="A258" s="6"/>
